--- a/통합 문서1.xlsx
+++ b/통합 문서1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BE7FFC5-D51F-4805-897C-814456F629E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A37B1C-A1FA-4BC8-ACA4-8F6F320D677B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{642C37AE-6014-445F-9D13-CBF516708FD7}"/>
+    <workbookView xWindow="0" yWindow="615" windowWidth="28800" windowHeight="15585" xr2:uid="{642C37AE-6014-445F-9D13-CBF516708FD7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -617,6 +617,10 @@
         <f>SUM(G1:G8)</f>
         <v>775020</v>
       </c>
+      <c r="J9">
+        <f>SUM(J2:J6)</f>
+        <v>699400</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
